--- a/results_report.xlsx
+++ b/results_report.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col width="13.24" customWidth="1" style="4" min="1" max="1"/>
@@ -1397,44 +1397,758 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>2605TL000009BESI</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>000009</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>خطأ: الصورة '2605TL000009BESI_0.png' غير موجودة في فولدر 'result_images'</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>خطأ: الصورة '2605TL000009BESI_1.png' غير موجودة في فولدر 'result_images'</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>خطأ: الصورة '2605TL000009BESI_2.png' غير موجودة في فولدر 'result_images'</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="0" t="inlineStr">
         <is>
           <t>خطأ: الصورة '2605TL000009BESI_3.png' غير موجودة في فولدر 'result_images'</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
         <is>
           <t>2026-05-17 14:44:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000001BESI</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>000001</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:16:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000009BESI</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>000009</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:17:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000001BESI</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>000001</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F26" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:18:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000001BESI</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>000001</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F27" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000001BESI</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>000001</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:44:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000009BESI</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>000009</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F29" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:45:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000001BESI</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>000001</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F30" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:45:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000009BESI</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>000009</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F31" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:45:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000001BESI</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>000001</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F32" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:45:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000009BESI</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>000009</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F33" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:45:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000009BESI</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t>000009</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D34" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F34" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:47:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000001BESI</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>000001</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F35" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H35" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:47:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000009BESI</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>000009</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D36" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F36" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H36" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:47:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000001BESI</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>000001</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F37" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H37" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:48:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000009BESI</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>000009</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F38" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H38" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:48:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>2605TL000001BESI</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>000001</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F39" s="0" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000001BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:48:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2605TL000009BESI</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>000009</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_0.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_1.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_2.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>خطأ: الصورة '2605TL000009BESI_3.png' غير موجودة في فولدر 'result_images'</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:48:54</t>
         </is>
       </c>
     </row>

--- a/results_report.xlsx
+++ b/results_report.xlsx
@@ -576,6 +576,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -601,6 +604,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -626,6 +632,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -651,6 +660,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -670,6 +682,834 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId49"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -972,7 +1812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1314,6 +2154,138 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="105" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2511TL005663ISI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>005663</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:27:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="105" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2511TL005663ISI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>005663</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:31:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="105" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2511TL005663ISI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>005663</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="105" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2511TL005663ISI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>005663</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-01 10:04:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="105" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2511TL005663ISI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>005663</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-06-01 10:24:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="105" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2511TL005663ISI</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>005663</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-06-01 10:30:44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/results_report.xlsx
+++ b/results_report.xlsx
@@ -436,6 +436,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -461,6 +464,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -480,6 +486,84 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -782,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -919,6 +1003,28 @@
         </is>
       </c>
     </row>
+    <row r="6" ht="105" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2511TL005663ISI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>005663</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:40:18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
